--- a/Server/temp.xlsx
+++ b/Server/temp.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K87"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -437,7 +437,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>20694306041</v>
+        <v>84209161173</v>
       </c>
       <c r="B2">
         <v>16</v>
@@ -452,7 +452,7 @@
         <v>330000</v>
       </c>
       <c r="F2" s="1">
-        <v>45793.999814814815</v>
+        <v>45750.999814814815</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -469,13 +469,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>89573999729</v>
+        <v>23707650229</v>
       </c>
       <c r="B3">
         <v>16</v>
       </c>
       <c r="C3" t="str">
-        <v>approved</v>
+        <v>rejected</v>
       </c>
       <c r="D3" t="str">
         <v>380000</v>
@@ -484,7 +484,7 @@
         <v>330000</v>
       </c>
       <c r="F3" s="1">
-        <v>45763.999814814815</v>
+        <v>45872.999814814815</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -501,13 +501,13 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>20284508723</v>
+        <v>75120387457</v>
       </c>
       <c r="B4">
         <v>16</v>
       </c>
       <c r="C4" t="str">
-        <v>approved</v>
+        <v>pending</v>
       </c>
       <c r="D4" t="str">
         <v>380000</v>
@@ -516,7 +516,7 @@
         <v>330000</v>
       </c>
       <c r="F4" s="1">
-        <v>45763.999814814815</v>
+        <v>45751.999814814815</v>
       </c>
       <c r="G4">
         <v>3</v>
@@ -533,7 +533,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>02280873377</v>
+        <v>20694306041</v>
       </c>
       <c r="B5">
         <v>16</v>
@@ -548,7 +548,7 @@
         <v>330000</v>
       </c>
       <c r="F5" s="1">
-        <v>45763.999814814815</v>
+        <v>45793.999814814815</v>
       </c>
       <c r="G5">
         <v>4</v>
@@ -565,13 +565,13 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>14234033154</v>
+        <v>34413851919</v>
       </c>
       <c r="B6">
         <v>16</v>
       </c>
       <c r="C6" t="str">
-        <v>approved</v>
+        <v>rejected</v>
       </c>
       <c r="D6" t="str">
         <v>380000</v>
@@ -580,7 +580,7 @@
         <v>330000</v>
       </c>
       <c r="F6" s="1">
-        <v>45770.999814814815</v>
+        <v>45799.999814814815</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -597,7 +597,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>18491577090</v>
+        <v>89573999729</v>
       </c>
       <c r="B7">
         <v>16</v>
@@ -612,7 +612,7 @@
         <v>330000</v>
       </c>
       <c r="F7" s="1">
-        <v>45767.999814814815</v>
+        <v>45763.999814814815</v>
       </c>
       <c r="G7">
         <v>6</v>
@@ -629,13 +629,13 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>42066676539</v>
+        <v>46509182042</v>
       </c>
       <c r="B8">
         <v>16</v>
       </c>
       <c r="C8" t="str">
-        <v>pending</v>
+        <v>rejected</v>
       </c>
       <c r="D8" t="str">
         <v>380000</v>
@@ -644,7 +644,7 @@
         <v>330000</v>
       </c>
       <c r="F8" s="1">
-        <v>45769.999814814815</v>
+        <v>45782.999814814815</v>
       </c>
       <c r="G8">
         <v>7</v>
@@ -661,7 +661,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>93250792386</v>
+        <v>20284508723</v>
       </c>
       <c r="B9">
         <v>16</v>
@@ -676,7 +676,7 @@
         <v>330000</v>
       </c>
       <c r="F9" s="1">
-        <v>45770.999814814815</v>
+        <v>45763.999814814815</v>
       </c>
       <c r="G9">
         <v>8</v>
@@ -693,13 +693,13 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>43967218603</v>
+        <v>89866331198</v>
       </c>
       <c r="B10">
         <v>16</v>
       </c>
       <c r="C10" t="str">
-        <v>approved</v>
+        <v>pending</v>
       </c>
       <c r="D10" t="str">
         <v>380000</v>
@@ -708,7 +708,7 @@
         <v>330000</v>
       </c>
       <c r="F10" s="1">
-        <v>45780.999814814815</v>
+        <v>45762.999814814815</v>
       </c>
       <c r="G10">
         <v>9</v>
@@ -725,13 +725,13 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>12630891458</v>
+        <v>98767893877</v>
       </c>
       <c r="B11">
         <v>16</v>
       </c>
       <c r="C11" t="str">
-        <v>approved</v>
+        <v>rejected</v>
       </c>
       <c r="D11" t="str">
         <v>380000</v>
@@ -740,7 +740,7 @@
         <v>330000</v>
       </c>
       <c r="F11" s="1">
-        <v>45822.999814814815</v>
+        <v>45782.999814814815</v>
       </c>
       <c r="G11">
         <v>10</v>
@@ -757,13 +757,13 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>78506968636</v>
+        <v>32975616478</v>
       </c>
       <c r="B12">
         <v>16</v>
       </c>
       <c r="C12" t="str">
-        <v>pending</v>
+        <v>approved</v>
       </c>
       <c r="D12" t="str">
         <v>380000</v>
@@ -772,7 +772,7 @@
         <v>330000</v>
       </c>
       <c r="F12" s="1">
-        <v>45776.999814814815</v>
+        <v>45842.999814814815</v>
       </c>
       <c r="G12">
         <v>11</v>
@@ -789,39 +789,2407 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>17515393585</v>
+        <v>08556434378</v>
       </c>
       <c r="B13">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="C13" t="str">
         <v>approved</v>
       </c>
       <c r="D13" t="str">
-        <v>365000</v>
+        <v>380000</v>
       </c>
       <c r="E13" t="str">
         <v>330000</v>
       </c>
       <c r="F13" s="1">
-        <v>45775.999814814815</v>
+        <v>45781.999814814815</v>
       </c>
       <c r="G13">
         <v>12</v>
       </c>
       <c r="H13">
-        <v>35000</v>
+        <v>50000</v>
       </c>
       <c r="I13" t="str">
+        <v>Mangata system</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>14234033154</v>
+      </c>
+      <c r="B14">
+        <v>16</v>
+      </c>
+      <c r="C14" t="str">
+        <v>approved</v>
+      </c>
+      <c r="D14" t="str">
+        <v>380000</v>
+      </c>
+      <c r="E14" t="str">
+        <v>330000</v>
+      </c>
+      <c r="F14" s="1">
+        <v>45770.999814814815</v>
+      </c>
+      <c r="G14">
+        <v>13</v>
+      </c>
+      <c r="H14">
+        <v>50000</v>
+      </c>
+      <c r="I14" t="str">
+        <v>Mangata system</v>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>02280873377</v>
+      </c>
+      <c r="B15">
+        <v>16</v>
+      </c>
+      <c r="C15" t="str">
+        <v>pending</v>
+      </c>
+      <c r="D15" t="str">
+        <v>380000</v>
+      </c>
+      <c r="E15" t="str">
+        <v>330000</v>
+      </c>
+      <c r="F15" s="1">
+        <v>45763.999814814815</v>
+      </c>
+      <c r="G15">
+        <v>14</v>
+      </c>
+      <c r="H15">
+        <v>50000</v>
+      </c>
+      <c r="I15" t="str">
+        <v>Mangata system</v>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>18491577090</v>
+      </c>
+      <c r="B16">
+        <v>16</v>
+      </c>
+      <c r="C16" t="str">
+        <v>approved</v>
+      </c>
+      <c r="D16" t="str">
+        <v>380000</v>
+      </c>
+      <c r="E16" t="str">
+        <v>330000</v>
+      </c>
+      <c r="F16" s="1">
+        <v>45767.999814814815</v>
+      </c>
+      <c r="G16">
+        <v>15</v>
+      </c>
+      <c r="H16">
+        <v>50000</v>
+      </c>
+      <c r="I16" t="str">
+        <v>Mangata system</v>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>42066676539</v>
+      </c>
+      <c r="B17">
+        <v>16</v>
+      </c>
+      <c r="C17" t="str">
+        <v>pending</v>
+      </c>
+      <c r="D17" t="str">
+        <v>380000</v>
+      </c>
+      <c r="E17" t="str">
+        <v>330000</v>
+      </c>
+      <c r="F17" s="1">
+        <v>45769.999814814815</v>
+      </c>
+      <c r="G17">
+        <v>16</v>
+      </c>
+      <c r="H17">
+        <v>50000</v>
+      </c>
+      <c r="I17" t="str">
+        <v>Mangata system</v>
+      </c>
+      <c r="J17" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>93250792386</v>
+      </c>
+      <c r="B18">
+        <v>16</v>
+      </c>
+      <c r="C18" t="str">
+        <v>approved</v>
+      </c>
+      <c r="D18" t="str">
+        <v>380000</v>
+      </c>
+      <c r="E18" t="str">
+        <v>330000</v>
+      </c>
+      <c r="F18" s="1">
+        <v>45770.999814814815</v>
+      </c>
+      <c r="G18">
+        <v>17</v>
+      </c>
+      <c r="H18">
+        <v>50000</v>
+      </c>
+      <c r="I18" t="str">
+        <v>Mangata system</v>
+      </c>
+      <c r="J18" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>99622526342</v>
+      </c>
+      <c r="B19">
+        <v>16</v>
+      </c>
+      <c r="C19" t="str">
+        <v>pending</v>
+      </c>
+      <c r="D19" t="str">
+        <v>380000</v>
+      </c>
+      <c r="E19" t="str">
+        <v>330000</v>
+      </c>
+      <c r="F19" s="1">
+        <v>45824.999814814815</v>
+      </c>
+      <c r="G19">
+        <v>18</v>
+      </c>
+      <c r="H19">
+        <v>50000</v>
+      </c>
+      <c r="I19" t="str">
+        <v>Mangata system</v>
+      </c>
+      <c r="J19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>43967218603</v>
+      </c>
+      <c r="B20">
+        <v>16</v>
+      </c>
+      <c r="C20" t="str">
+        <v>approved</v>
+      </c>
+      <c r="D20" t="str">
+        <v>380000</v>
+      </c>
+      <c r="E20" t="str">
+        <v>330000</v>
+      </c>
+      <c r="F20" s="1">
+        <v>45780.999814814815</v>
+      </c>
+      <c r="G20">
+        <v>19</v>
+      </c>
+      <c r="H20">
+        <v>50000</v>
+      </c>
+      <c r="I20" t="str">
+        <v>Mangata system</v>
+      </c>
+      <c r="J20" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>16925018223</v>
+      </c>
+      <c r="B21">
+        <v>16</v>
+      </c>
+      <c r="C21" t="str">
+        <v>approved</v>
+      </c>
+      <c r="D21" t="str">
+        <v>380000</v>
+      </c>
+      <c r="E21" t="str">
+        <v>330000</v>
+      </c>
+      <c r="F21" s="1">
+        <v>45789.999814814815</v>
+      </c>
+      <c r="G21">
+        <v>20</v>
+      </c>
+      <c r="H21">
+        <v>50000</v>
+      </c>
+      <c r="I21" t="str">
+        <v>Mangata system</v>
+      </c>
+      <c r="J21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>12630891458</v>
+      </c>
+      <c r="B22">
+        <v>16</v>
+      </c>
+      <c r="C22" t="str">
+        <v>approved</v>
+      </c>
+      <c r="D22" t="str">
+        <v>380000</v>
+      </c>
+      <c r="E22" t="str">
+        <v>330000</v>
+      </c>
+      <c r="F22" s="1">
+        <v>45822.999814814815</v>
+      </c>
+      <c r="G22">
+        <v>21</v>
+      </c>
+      <c r="H22">
+        <v>50000</v>
+      </c>
+      <c r="I22" t="str">
+        <v>Mangata system</v>
+      </c>
+      <c r="J22" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>60317804448</v>
+      </c>
+      <c r="B23">
+        <v>16</v>
+      </c>
+      <c r="C23" t="str">
+        <v>pending</v>
+      </c>
+      <c r="D23" t="str">
+        <v>380000</v>
+      </c>
+      <c r="E23" t="str">
+        <v>330000</v>
+      </c>
+      <c r="F23" s="1">
+        <v>45785.999814814815</v>
+      </c>
+      <c r="G23">
+        <v>22</v>
+      </c>
+      <c r="H23">
+        <v>50000</v>
+      </c>
+      <c r="I23" t="str">
+        <v>Mangata system</v>
+      </c>
+      <c r="J23" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>46834295581</v>
+      </c>
+      <c r="B24">
+        <v>16</v>
+      </c>
+      <c r="C24" t="str">
+        <v>approved</v>
+      </c>
+      <c r="D24" t="str">
+        <v>380000</v>
+      </c>
+      <c r="E24" t="str">
+        <v>330000</v>
+      </c>
+      <c r="F24" s="1">
+        <v>45799.999814814815</v>
+      </c>
+      <c r="G24">
+        <v>23</v>
+      </c>
+      <c r="H24">
+        <v>50000</v>
+      </c>
+      <c r="I24" t="str">
+        <v>Mangata system</v>
+      </c>
+      <c r="J24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>80119636522</v>
+      </c>
+      <c r="B25">
+        <v>16</v>
+      </c>
+      <c r="C25" t="str">
+        <v>approved</v>
+      </c>
+      <c r="D25" t="str">
+        <v>380000</v>
+      </c>
+      <c r="E25" t="str">
+        <v>330000</v>
+      </c>
+      <c r="F25" s="1">
+        <v>45842.999814814815</v>
+      </c>
+      <c r="G25">
+        <v>24</v>
+      </c>
+      <c r="H25">
+        <v>50000</v>
+      </c>
+      <c r="I25" t="str">
+        <v>Mangata system</v>
+      </c>
+      <c r="J25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>59209869725</v>
+      </c>
+      <c r="B26">
+        <v>16</v>
+      </c>
+      <c r="C26" t="str">
+        <v>pending</v>
+      </c>
+      <c r="D26" t="str">
+        <v>380000</v>
+      </c>
+      <c r="E26" t="str">
+        <v>330000</v>
+      </c>
+      <c r="F26" s="1">
+        <v>45786.999814814815</v>
+      </c>
+      <c r="G26">
+        <v>25</v>
+      </c>
+      <c r="H26">
+        <v>50000</v>
+      </c>
+      <c r="I26" t="str">
+        <v>Mangata system</v>
+      </c>
+      <c r="J26" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>98313659181</v>
+      </c>
+      <c r="B27">
+        <v>16</v>
+      </c>
+      <c r="C27" t="str">
+        <v>rejected</v>
+      </c>
+      <c r="D27" t="str">
+        <v>380000</v>
+      </c>
+      <c r="E27" t="str">
+        <v>330000</v>
+      </c>
+      <c r="F27" s="1">
+        <v>45782.999814814815</v>
+      </c>
+      <c r="G27">
+        <v>26</v>
+      </c>
+      <c r="H27">
+        <v>50000</v>
+      </c>
+      <c r="I27" t="str">
+        <v>Mangata system</v>
+      </c>
+      <c r="J27" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>39213837469</v>
+      </c>
+      <c r="B28">
+        <v>16</v>
+      </c>
+      <c r="C28" t="str">
+        <v>pending</v>
+      </c>
+      <c r="D28" t="str">
+        <v>380000</v>
+      </c>
+      <c r="E28" t="str">
+        <v>330000</v>
+      </c>
+      <c r="F28" s="1">
+        <v>45815.999814814815</v>
+      </c>
+      <c r="G28">
+        <v>27</v>
+      </c>
+      <c r="H28">
+        <v>50000</v>
+      </c>
+      <c r="I28" t="str">
+        <v>Mangata system</v>
+      </c>
+      <c r="J28" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>37315192421</v>
+      </c>
+      <c r="B29">
+        <v>16</v>
+      </c>
+      <c r="C29" t="str">
+        <v>pending</v>
+      </c>
+      <c r="D29" t="str">
+        <v>380000</v>
+      </c>
+      <c r="E29" t="str">
+        <v>330000</v>
+      </c>
+      <c r="F29" s="1">
+        <v>45789.999814814815</v>
+      </c>
+      <c r="G29">
+        <v>28</v>
+      </c>
+      <c r="H29">
+        <v>50000</v>
+      </c>
+      <c r="I29" t="str">
+        <v>Mangata system</v>
+      </c>
+      <c r="J29" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>23680022151</v>
+      </c>
+      <c r="B30">
+        <v>2</v>
+      </c>
+      <c r="C30" t="str">
+        <v>pending</v>
+      </c>
+      <c r="D30" t="str">
+        <v>380000</v>
+      </c>
+      <c r="E30" t="str">
+        <v>330000</v>
+      </c>
+      <c r="F30" s="1">
+        <v>45750.999814814815</v>
+      </c>
+      <c r="G30">
+        <v>29</v>
+      </c>
+      <c r="H30">
+        <v>50000</v>
+      </c>
+      <c r="I30" t="str">
         <v>Carlos Taborda</v>
       </c>
-      <c r="J13" t="str">
-        <v>123456</v>
+      <c r="J30" t="str">
+        <v>02932562211</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>78732679275</v>
+      </c>
+      <c r="B31">
+        <v>16</v>
+      </c>
+      <c r="C31" t="str">
+        <v>pending</v>
+      </c>
+      <c r="D31" t="str">
+        <v>380000</v>
+      </c>
+      <c r="E31" t="str">
+        <v>330000</v>
+      </c>
+      <c r="F31" s="1">
+        <v>45860.999814814815</v>
+      </c>
+      <c r="G31">
+        <v>30</v>
+      </c>
+      <c r="H31">
+        <v>50000</v>
+      </c>
+      <c r="I31" t="str">
+        <v>Mangata system</v>
+      </c>
+      <c r="J31" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>56092874982</v>
+      </c>
+      <c r="B32">
+        <v>16</v>
+      </c>
+      <c r="C32" t="str">
+        <v>rejected</v>
+      </c>
+      <c r="D32" t="str">
+        <v>380000</v>
+      </c>
+      <c r="E32" t="str">
+        <v>330000</v>
+      </c>
+      <c r="F32" s="1">
+        <v>45799.999814814815</v>
+      </c>
+      <c r="G32">
+        <v>31</v>
+      </c>
+      <c r="H32">
+        <v>50000</v>
+      </c>
+      <c r="I32" t="str">
+        <v>Mangata system</v>
+      </c>
+      <c r="J32" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>93667164510</v>
+      </c>
+      <c r="B33">
+        <v>16</v>
+      </c>
+      <c r="C33" t="str">
+        <v>approved</v>
+      </c>
+      <c r="D33" t="str">
+        <v>380000</v>
+      </c>
+      <c r="E33" t="str">
+        <v>330000</v>
+      </c>
+      <c r="F33" s="1">
+        <v>45799.999814814815</v>
+      </c>
+      <c r="G33">
+        <v>32</v>
+      </c>
+      <c r="H33">
+        <v>50000</v>
+      </c>
+      <c r="I33" t="str">
+        <v>Mangata system</v>
+      </c>
+      <c r="J33" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>47676188822</v>
+      </c>
+      <c r="B34">
+        <v>16</v>
+      </c>
+      <c r="C34" t="str">
+        <v>pending</v>
+      </c>
+      <c r="D34" t="str">
+        <v>380000</v>
+      </c>
+      <c r="E34" t="str">
+        <v>330000</v>
+      </c>
+      <c r="F34" s="1">
+        <v>45860.999814814815</v>
+      </c>
+      <c r="G34">
+        <v>33</v>
+      </c>
+      <c r="H34">
+        <v>50000</v>
+      </c>
+      <c r="I34" t="str">
+        <v>Mangata system</v>
+      </c>
+      <c r="J34" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>27890511484</v>
+      </c>
+      <c r="B35">
+        <v>16</v>
+      </c>
+      <c r="C35" t="str">
+        <v>rejected</v>
+      </c>
+      <c r="D35" t="str">
+        <v>380000</v>
+      </c>
+      <c r="E35" t="str">
+        <v>330000</v>
+      </c>
+      <c r="F35" s="1">
+        <v>45799.999814814815</v>
+      </c>
+      <c r="G35">
+        <v>34</v>
+      </c>
+      <c r="H35">
+        <v>50000</v>
+      </c>
+      <c r="I35" t="str">
+        <v>Mangata system</v>
+      </c>
+      <c r="J35" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>90708693174</v>
+      </c>
+      <c r="B36">
+        <v>16</v>
+      </c>
+      <c r="C36" t="str">
+        <v>pending</v>
+      </c>
+      <c r="D36" t="str">
+        <v>380000</v>
+      </c>
+      <c r="E36" t="str">
+        <v>330000</v>
+      </c>
+      <c r="F36" s="1">
+        <v>45799.999814814815</v>
+      </c>
+      <c r="G36">
+        <v>35</v>
+      </c>
+      <c r="H36">
+        <v>50000</v>
+      </c>
+      <c r="I36" t="str">
+        <v>Mangata system</v>
+      </c>
+      <c r="J36" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>66840357294</v>
+      </c>
+      <c r="B37">
+        <v>16</v>
+      </c>
+      <c r="C37" t="str">
+        <v>pending</v>
+      </c>
+      <c r="D37" t="str">
+        <v>380000</v>
+      </c>
+      <c r="E37" t="str">
+        <v>330000</v>
+      </c>
+      <c r="F37" s="1">
+        <v>45846.999814814815</v>
+      </c>
+      <c r="G37">
+        <v>36</v>
+      </c>
+      <c r="H37">
+        <v>50000</v>
+      </c>
+      <c r="I37" t="str">
+        <v>Mangata system</v>
+      </c>
+      <c r="J37" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>55810766153</v>
+      </c>
+      <c r="B38">
+        <v>16</v>
+      </c>
+      <c r="C38" t="str">
+        <v>pending</v>
+      </c>
+      <c r="D38" t="str">
+        <v>380000</v>
+      </c>
+      <c r="E38" t="str">
+        <v>330000</v>
+      </c>
+      <c r="F38" s="1">
+        <v>45800.999814814815</v>
+      </c>
+      <c r="G38">
+        <v>37</v>
+      </c>
+      <c r="H38">
+        <v>50000</v>
+      </c>
+      <c r="I38" t="str">
+        <v>Mangata system</v>
+      </c>
+      <c r="J38" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>10395083312</v>
+      </c>
+      <c r="B39">
+        <v>16</v>
+      </c>
+      <c r="C39" t="str">
+        <v>pending</v>
+      </c>
+      <c r="D39" t="str">
+        <v>380000</v>
+      </c>
+      <c r="E39" t="str">
+        <v>330000</v>
+      </c>
+      <c r="F39" s="1">
+        <v>45800.999814814815</v>
+      </c>
+      <c r="G39">
+        <v>38</v>
+      </c>
+      <c r="H39">
+        <v>50000</v>
+      </c>
+      <c r="I39" t="str">
+        <v>Mangata system</v>
+      </c>
+      <c r="J39" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>44495745601</v>
+      </c>
+      <c r="B40">
+        <v>16</v>
+      </c>
+      <c r="C40" t="str">
+        <v>pending</v>
+      </c>
+      <c r="D40" t="str">
+        <v>380000</v>
+      </c>
+      <c r="E40" t="str">
+        <v>330000</v>
+      </c>
+      <c r="F40" s="1">
+        <v>45840.999814814815</v>
+      </c>
+      <c r="G40">
+        <v>39</v>
+      </c>
+      <c r="H40">
+        <v>50000</v>
+      </c>
+      <c r="I40" t="str">
+        <v>Mangata system</v>
+      </c>
+      <c r="J40" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>64556646971</v>
+      </c>
+      <c r="B41">
+        <v>16</v>
+      </c>
+      <c r="C41" t="str">
+        <v>pending</v>
+      </c>
+      <c r="D41" t="str">
+        <v>380000</v>
+      </c>
+      <c r="E41" t="str">
+        <v>330000</v>
+      </c>
+      <c r="F41" s="1">
+        <v>45811.999814814815</v>
+      </c>
+      <c r="G41">
+        <v>40</v>
+      </c>
+      <c r="H41">
+        <v>50000</v>
+      </c>
+      <c r="I41" t="str">
+        <v>Mangata system</v>
+      </c>
+      <c r="J41" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>71025145605</v>
+      </c>
+      <c r="B42">
+        <v>16</v>
+      </c>
+      <c r="C42" t="str">
+        <v>approved</v>
+      </c>
+      <c r="D42" t="str">
+        <v>380000</v>
+      </c>
+      <c r="E42" t="str">
+        <v>330000</v>
+      </c>
+      <c r="F42" s="1">
+        <v>45810.999814814815</v>
+      </c>
+      <c r="G42">
+        <v>41</v>
+      </c>
+      <c r="H42">
+        <v>50000</v>
+      </c>
+      <c r="I42" t="str">
+        <v>Mangata system</v>
+      </c>
+      <c r="J42" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>12600053793</v>
+      </c>
+      <c r="B43">
+        <v>16</v>
+      </c>
+      <c r="C43" t="str">
+        <v>pending</v>
+      </c>
+      <c r="D43" t="str">
+        <v>380000</v>
+      </c>
+      <c r="E43" t="str">
+        <v>330000</v>
+      </c>
+      <c r="F43" s="1">
+        <v>45813.999814814815</v>
+      </c>
+      <c r="G43">
+        <v>42</v>
+      </c>
+      <c r="H43">
+        <v>50000</v>
+      </c>
+      <c r="I43" t="str">
+        <v>Mangata system</v>
+      </c>
+      <c r="J43" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>36511469307</v>
+      </c>
+      <c r="B44">
+        <v>16</v>
+      </c>
+      <c r="C44" t="str">
+        <v>pending</v>
+      </c>
+      <c r="D44" t="str">
+        <v>380000</v>
+      </c>
+      <c r="E44" t="str">
+        <v>330000</v>
+      </c>
+      <c r="F44" s="1">
+        <v>45821.999814814815</v>
+      </c>
+      <c r="G44">
+        <v>43</v>
+      </c>
+      <c r="H44">
+        <v>50000</v>
+      </c>
+      <c r="I44" t="str">
+        <v>Mangata system</v>
+      </c>
+      <c r="J44" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>29072483641</v>
+      </c>
+      <c r="B45">
+        <v>16</v>
+      </c>
+      <c r="C45" t="str">
+        <v>pending</v>
+      </c>
+      <c r="D45" t="str">
+        <v>380000</v>
+      </c>
+      <c r="E45" t="str">
+        <v>330000</v>
+      </c>
+      <c r="F45" s="1">
+        <v>45832.999814814815</v>
+      </c>
+      <c r="G45">
+        <v>44</v>
+      </c>
+      <c r="H45">
+        <v>50000</v>
+      </c>
+      <c r="I45" t="str">
+        <v>Mangata system</v>
+      </c>
+      <c r="J45" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>45568299865</v>
+      </c>
+      <c r="B46">
+        <v>16</v>
+      </c>
+      <c r="C46" t="str">
+        <v>approved</v>
+      </c>
+      <c r="D46" t="str">
+        <v>380000</v>
+      </c>
+      <c r="E46" t="str">
+        <v>330000</v>
+      </c>
+      <c r="F46" s="1">
+        <v>45862.999814814815</v>
+      </c>
+      <c r="G46">
+        <v>45</v>
+      </c>
+      <c r="H46">
+        <v>50000</v>
+      </c>
+      <c r="I46" t="str">
+        <v>Mangata system</v>
+      </c>
+      <c r="J46" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>04478769736</v>
+      </c>
+      <c r="B47">
+        <v>16</v>
+      </c>
+      <c r="C47" t="str">
+        <v>pending</v>
+      </c>
+      <c r="D47" t="str">
+        <v>380000</v>
+      </c>
+      <c r="E47" t="str">
+        <v>330000</v>
+      </c>
+      <c r="F47" s="1">
+        <v>45853.999814814815</v>
+      </c>
+      <c r="G47">
+        <v>46</v>
+      </c>
+      <c r="H47">
+        <v>50000</v>
+      </c>
+      <c r="I47" t="str">
+        <v>Mangata system</v>
+      </c>
+      <c r="J47" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>19863375976</v>
+      </c>
+      <c r="B48">
+        <v>16</v>
+      </c>
+      <c r="C48" t="str">
+        <v>pending</v>
+      </c>
+      <c r="D48" t="str">
+        <v>380000</v>
+      </c>
+      <c r="E48" t="str">
+        <v>330000</v>
+      </c>
+      <c r="F48" s="1">
+        <v>45853.999814814815</v>
+      </c>
+      <c r="G48">
+        <v>47</v>
+      </c>
+      <c r="H48">
+        <v>50000</v>
+      </c>
+      <c r="I48" t="str">
+        <v>Mangata system</v>
+      </c>
+      <c r="J48" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>18073197655</v>
+      </c>
+      <c r="B49">
+        <v>16</v>
+      </c>
+      <c r="C49" t="str">
+        <v>pending</v>
+      </c>
+      <c r="D49" t="str">
+        <v>380000</v>
+      </c>
+      <c r="E49" t="str">
+        <v>330000</v>
+      </c>
+      <c r="F49" s="1">
+        <v>45858.999814814815</v>
+      </c>
+      <c r="G49">
+        <v>48</v>
+      </c>
+      <c r="H49">
+        <v>50000</v>
+      </c>
+      <c r="I49" t="str">
+        <v>Mangata system</v>
+      </c>
+      <c r="J49" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>01063079928</v>
+      </c>
+      <c r="B50">
+        <v>16</v>
+      </c>
+      <c r="C50" t="str">
+        <v>pending</v>
+      </c>
+      <c r="D50" t="str">
+        <v>380000</v>
+      </c>
+      <c r="E50" t="str">
+        <v>330000</v>
+      </c>
+      <c r="F50" s="1">
+        <v>45863.999814814815</v>
+      </c>
+      <c r="G50">
+        <v>49</v>
+      </c>
+      <c r="H50">
+        <v>50000</v>
+      </c>
+      <c r="I50" t="str">
+        <v>Mangata system</v>
+      </c>
+      <c r="J50" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>23336076956</v>
+      </c>
+      <c r="B51">
+        <v>16</v>
+      </c>
+      <c r="C51" t="str">
+        <v>pending</v>
+      </c>
+      <c r="D51" t="str">
+        <v>380000</v>
+      </c>
+      <c r="E51" t="str">
+        <v>330000</v>
+      </c>
+      <c r="F51" s="1">
+        <v>45869.999814814815</v>
+      </c>
+      <c r="G51">
+        <v>50</v>
+      </c>
+      <c r="H51">
+        <v>50000</v>
+      </c>
+      <c r="I51" t="str">
+        <v>Mangata system</v>
+      </c>
+      <c r="J51" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>68610928817</v>
+      </c>
+      <c r="B52">
+        <v>16</v>
+      </c>
+      <c r="C52" t="str">
+        <v>pending</v>
+      </c>
+      <c r="D52" t="str">
+        <v>380000</v>
+      </c>
+      <c r="E52" t="str">
+        <v>330000</v>
+      </c>
+      <c r="F52" s="1">
+        <v>45878.999814814815</v>
+      </c>
+      <c r="G52">
+        <v>51</v>
+      </c>
+      <c r="H52">
+        <v>50000</v>
+      </c>
+      <c r="I52" t="str">
+        <v>Mangata system</v>
+      </c>
+      <c r="J52" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>00532929706</v>
+      </c>
+      <c r="B53">
+        <v>16</v>
+      </c>
+      <c r="C53" t="str">
+        <v>pending</v>
+      </c>
+      <c r="D53" t="str">
+        <v>380000</v>
+      </c>
+      <c r="E53" t="str">
+        <v>330000</v>
+      </c>
+      <c r="F53" s="1">
+        <v>45878.999814814815</v>
+      </c>
+      <c r="G53">
+        <v>52</v>
+      </c>
+      <c r="H53">
+        <v>50000</v>
+      </c>
+      <c r="I53" t="str">
+        <v>Mangata system</v>
+      </c>
+      <c r="J53" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>54081642396</v>
+      </c>
+      <c r="B54">
+        <v>16</v>
+      </c>
+      <c r="C54" t="str">
+        <v>pending</v>
+      </c>
+      <c r="D54" t="str">
+        <v>380000</v>
+      </c>
+      <c r="E54" t="str">
+        <v>330000</v>
+      </c>
+      <c r="F54" s="1">
+        <v>45878.999814814815</v>
+      </c>
+      <c r="G54">
+        <v>53</v>
+      </c>
+      <c r="H54">
+        <v>50000</v>
+      </c>
+      <c r="I54" t="str">
+        <v>Mangata system</v>
+      </c>
+      <c r="J54" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>71977118012</v>
+      </c>
+      <c r="B55">
+        <v>16</v>
+      </c>
+      <c r="C55" t="str">
+        <v>approved</v>
+      </c>
+      <c r="D55" t="str">
+        <v>380000</v>
+      </c>
+      <c r="E55" t="str">
+        <v>330000</v>
+      </c>
+      <c r="F55" s="1">
+        <v>45889.999814814815</v>
+      </c>
+      <c r="G55">
+        <v>54</v>
+      </c>
+      <c r="H55">
+        <v>50000</v>
+      </c>
+      <c r="I55" t="str">
+        <v>Mangata system</v>
+      </c>
+      <c r="J55" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>12320776143</v>
+      </c>
+      <c r="B56">
+        <v>16</v>
+      </c>
+      <c r="C56" t="str">
+        <v>approved</v>
+      </c>
+      <c r="D56" t="str">
+        <v>380000</v>
+      </c>
+      <c r="E56" t="str">
+        <v>330000</v>
+      </c>
+      <c r="F56" s="1">
+        <v>45875.999814814815</v>
+      </c>
+      <c r="G56">
+        <v>55</v>
+      </c>
+      <c r="H56">
+        <v>50000</v>
+      </c>
+      <c r="I56" t="str">
+        <v>Mangata system</v>
+      </c>
+      <c r="J56" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>03672853638</v>
+      </c>
+      <c r="B57">
+        <v>16</v>
+      </c>
+      <c r="C57" t="str">
+        <v>approved</v>
+      </c>
+      <c r="D57" t="str">
+        <v>380000</v>
+      </c>
+      <c r="E57" t="str">
+        <v>330000</v>
+      </c>
+      <c r="F57" s="1">
+        <v>45877.999814814815</v>
+      </c>
+      <c r="G57">
+        <v>56</v>
+      </c>
+      <c r="H57">
+        <v>50000</v>
+      </c>
+      <c r="I57" t="str">
+        <v>Mangata system</v>
+      </c>
+      <c r="J57" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>14366742633</v>
+      </c>
+      <c r="B58">
+        <v>16</v>
+      </c>
+      <c r="C58" t="str">
+        <v>approved</v>
+      </c>
+      <c r="D58" t="str">
+        <v>380000</v>
+      </c>
+      <c r="E58" t="str">
+        <v>330000</v>
+      </c>
+      <c r="F58" s="1">
+        <v>45899.999814814815</v>
+      </c>
+      <c r="G58">
+        <v>57</v>
+      </c>
+      <c r="H58">
+        <v>50000</v>
+      </c>
+      <c r="I58" t="str">
+        <v>Mangata system</v>
+      </c>
+      <c r="J58" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>85998650305</v>
+      </c>
+      <c r="B59">
+        <v>16</v>
+      </c>
+      <c r="C59" t="str">
+        <v>pending</v>
+      </c>
+      <c r="D59" t="str">
+        <v>380000</v>
+      </c>
+      <c r="E59" t="str">
+        <v>330000</v>
+      </c>
+      <c r="F59" s="1">
+        <v>45908.999814814815</v>
+      </c>
+      <c r="G59">
+        <v>58</v>
+      </c>
+      <c r="H59">
+        <v>50000</v>
+      </c>
+      <c r="I59" t="str">
+        <v>Mangata system</v>
+      </c>
+      <c r="J59" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>42321237446</v>
+      </c>
+      <c r="B60">
+        <v>16</v>
+      </c>
+      <c r="C60" t="str">
+        <v>pending</v>
+      </c>
+      <c r="D60" t="str">
+        <v>380000</v>
+      </c>
+      <c r="E60" t="str">
+        <v>330000</v>
+      </c>
+      <c r="F60" s="1">
+        <v>45884.999814814815</v>
+      </c>
+      <c r="G60">
+        <v>59</v>
+      </c>
+      <c r="H60">
+        <v>50000</v>
+      </c>
+      <c r="I60" t="str">
+        <v>Mangata system</v>
+      </c>
+      <c r="J60" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>38560069830</v>
+      </c>
+      <c r="B61">
+        <v>16</v>
+      </c>
+      <c r="C61" t="str">
+        <v>pending</v>
+      </c>
+      <c r="D61" t="str">
+        <v>380000</v>
+      </c>
+      <c r="E61" t="str">
+        <v>330000</v>
+      </c>
+      <c r="F61" s="1">
+        <v>45884.999814814815</v>
+      </c>
+      <c r="G61">
+        <v>60</v>
+      </c>
+      <c r="H61">
+        <v>50000</v>
+      </c>
+      <c r="I61" t="str">
+        <v>Mangata system</v>
+      </c>
+      <c r="J61" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>76847131262</v>
+      </c>
+      <c r="B62">
+        <v>16</v>
+      </c>
+      <c r="C62" t="str">
+        <v>pending</v>
+      </c>
+      <c r="D62" t="str">
+        <v>380000</v>
+      </c>
+      <c r="E62" t="str">
+        <v>330000</v>
+      </c>
+      <c r="F62" s="1">
+        <v>45891.999814814815</v>
+      </c>
+      <c r="G62">
+        <v>61</v>
+      </c>
+      <c r="H62">
+        <v>50000</v>
+      </c>
+      <c r="I62" t="str">
+        <v>Mangata system</v>
+      </c>
+      <c r="J62" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>34301136879</v>
+      </c>
+      <c r="B63">
+        <v>16</v>
+      </c>
+      <c r="C63" t="str">
+        <v>pending</v>
+      </c>
+      <c r="D63" t="str">
+        <v>380000</v>
+      </c>
+      <c r="E63" t="str">
+        <v>330000</v>
+      </c>
+      <c r="F63" s="1">
+        <v>45891.999814814815</v>
+      </c>
+      <c r="G63">
+        <v>62</v>
+      </c>
+      <c r="H63">
+        <v>50000</v>
+      </c>
+      <c r="I63" t="str">
+        <v>Mangata system</v>
+      </c>
+      <c r="J63" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>07337591897</v>
+      </c>
+      <c r="B64">
+        <v>16</v>
+      </c>
+      <c r="C64" t="str">
+        <v>pending</v>
+      </c>
+      <c r="D64" t="str">
+        <v>380000</v>
+      </c>
+      <c r="E64" t="str">
+        <v>330000</v>
+      </c>
+      <c r="F64" s="1">
+        <v>45892.999814814815</v>
+      </c>
+      <c r="G64">
+        <v>63</v>
+      </c>
+      <c r="H64">
+        <v>50000</v>
+      </c>
+      <c r="I64" t="str">
+        <v>Mangata system</v>
+      </c>
+      <c r="J64" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>61062448569</v>
+      </c>
+      <c r="B65">
+        <v>16</v>
+      </c>
+      <c r="C65" t="str">
+        <v>pending</v>
+      </c>
+      <c r="D65" t="str">
+        <v>380000</v>
+      </c>
+      <c r="E65" t="str">
+        <v>330000</v>
+      </c>
+      <c r="F65" s="1">
+        <v>45891.999814814815</v>
+      </c>
+      <c r="G65">
+        <v>64</v>
+      </c>
+      <c r="H65">
+        <v>50000</v>
+      </c>
+      <c r="I65" t="str">
+        <v>Mangata system</v>
+      </c>
+      <c r="J65" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>21352430883</v>
+      </c>
+      <c r="B66">
+        <v>16</v>
+      </c>
+      <c r="C66" t="str">
+        <v>pending</v>
+      </c>
+      <c r="D66" t="str">
+        <v>380000</v>
+      </c>
+      <c r="E66" t="str">
+        <v>330000</v>
+      </c>
+      <c r="F66" s="1">
+        <v>45886.999814814815</v>
+      </c>
+      <c r="G66">
+        <v>65</v>
+      </c>
+      <c r="H66">
+        <v>50000</v>
+      </c>
+      <c r="I66" t="str">
+        <v>Mangata system</v>
+      </c>
+      <c r="J66" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>65201916488</v>
+      </c>
+      <c r="B67">
+        <v>16</v>
+      </c>
+      <c r="C67" t="str">
+        <v>pending</v>
+      </c>
+      <c r="D67" t="str">
+        <v>380000</v>
+      </c>
+      <c r="E67" t="str">
+        <v>330000</v>
+      </c>
+      <c r="F67" s="1">
+        <v>45887.999814814815</v>
+      </c>
+      <c r="G67">
+        <v>66</v>
+      </c>
+      <c r="H67">
+        <v>50000</v>
+      </c>
+      <c r="I67" t="str">
+        <v>Mangata system</v>
+      </c>
+      <c r="J67" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>32385331380</v>
+      </c>
+      <c r="B68">
+        <v>16</v>
+      </c>
+      <c r="C68" t="str">
+        <v>pending</v>
+      </c>
+      <c r="D68" t="str">
+        <v>380000</v>
+      </c>
+      <c r="E68" t="str">
+        <v>330000</v>
+      </c>
+      <c r="F68" s="1">
+        <v>45887.999814814815</v>
+      </c>
+      <c r="G68">
+        <v>67</v>
+      </c>
+      <c r="H68">
+        <v>50000</v>
+      </c>
+      <c r="I68" t="str">
+        <v>Mangata system</v>
+      </c>
+      <c r="J68" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>61699997766</v>
+      </c>
+      <c r="B69">
+        <v>16</v>
+      </c>
+      <c r="C69" t="str">
+        <v>pending</v>
+      </c>
+      <c r="D69" t="str">
+        <v>380000</v>
+      </c>
+      <c r="E69" t="str">
+        <v>330000</v>
+      </c>
+      <c r="F69" s="1">
+        <v>45887.999814814815</v>
+      </c>
+      <c r="G69">
+        <v>68</v>
+      </c>
+      <c r="H69">
+        <v>50000</v>
+      </c>
+      <c r="I69" t="str">
+        <v>Mangata system</v>
+      </c>
+      <c r="J69" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>34263760118</v>
+      </c>
+      <c r="B70">
+        <v>16</v>
+      </c>
+      <c r="C70" t="str">
+        <v>pending</v>
+      </c>
+      <c r="D70" t="str">
+        <v>380000</v>
+      </c>
+      <c r="E70" t="str">
+        <v>330000</v>
+      </c>
+      <c r="F70" s="1">
+        <v>45887.999814814815</v>
+      </c>
+      <c r="G70">
+        <v>69</v>
+      </c>
+      <c r="H70">
+        <v>50000</v>
+      </c>
+      <c r="I70" t="str">
+        <v>Mangata system</v>
+      </c>
+      <c r="J70" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>98950232718</v>
+      </c>
+      <c r="B71">
+        <v>16</v>
+      </c>
+      <c r="C71" t="str">
+        <v>approved</v>
+      </c>
+      <c r="D71" t="str">
+        <v>380000</v>
+      </c>
+      <c r="E71" t="str">
+        <v>330000</v>
+      </c>
+      <c r="F71" s="1">
+        <v>45891.999814814815</v>
+      </c>
+      <c r="G71">
+        <v>70</v>
+      </c>
+      <c r="H71">
+        <v>50000</v>
+      </c>
+      <c r="I71" t="str">
+        <v>Mangata system</v>
+      </c>
+      <c r="J71" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>55087392567</v>
+      </c>
+      <c r="B72">
+        <v>16</v>
+      </c>
+      <c r="C72" t="str">
+        <v>approved</v>
+      </c>
+      <c r="D72" t="str">
+        <v>380000</v>
+      </c>
+      <c r="E72" t="str">
+        <v>330000</v>
+      </c>
+      <c r="F72" s="1">
+        <v>45891.999814814815</v>
+      </c>
+      <c r="G72">
+        <v>71</v>
+      </c>
+      <c r="H72">
+        <v>50000</v>
+      </c>
+      <c r="I72" t="str">
+        <v>Mangata system</v>
+      </c>
+      <c r="J72" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>52265196788</v>
+      </c>
+      <c r="B73">
+        <v>16</v>
+      </c>
+      <c r="C73" t="str">
+        <v>approved</v>
+      </c>
+      <c r="D73" t="str">
+        <v>380000</v>
+      </c>
+      <c r="E73" t="str">
+        <v>330000</v>
+      </c>
+      <c r="F73" s="1">
+        <v>45891.999814814815</v>
+      </c>
+      <c r="G73">
+        <v>72</v>
+      </c>
+      <c r="H73">
+        <v>50000</v>
+      </c>
+      <c r="I73" t="str">
+        <v>Mangata system</v>
+      </c>
+      <c r="J73" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>58511269165</v>
+      </c>
+      <c r="B74">
+        <v>16</v>
+      </c>
+      <c r="C74" t="str">
+        <v>approved</v>
+      </c>
+      <c r="D74" t="str">
+        <v>380000</v>
+      </c>
+      <c r="E74" t="str">
+        <v>330000</v>
+      </c>
+      <c r="F74" s="1">
+        <v>45891.999814814815</v>
+      </c>
+      <c r="G74">
+        <v>73</v>
+      </c>
+      <c r="H74">
+        <v>50000</v>
+      </c>
+      <c r="I74" t="str">
+        <v>Mangata system</v>
+      </c>
+      <c r="J74" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>00970750988</v>
+      </c>
+      <c r="B75">
+        <v>16</v>
+      </c>
+      <c r="C75" t="str">
+        <v>pending</v>
+      </c>
+      <c r="D75" t="str">
+        <v>380000</v>
+      </c>
+      <c r="E75" t="str">
+        <v>330000</v>
+      </c>
+      <c r="F75" s="1">
+        <v>45889.999814814815</v>
+      </c>
+      <c r="G75">
+        <v>74</v>
+      </c>
+      <c r="H75">
+        <v>50000</v>
+      </c>
+      <c r="I75" t="str">
+        <v>Mangata system</v>
+      </c>
+      <c r="J75" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>86984987507</v>
+      </c>
+      <c r="B76">
+        <v>16</v>
+      </c>
+      <c r="C76" t="str">
+        <v>pending</v>
+      </c>
+      <c r="D76" t="str">
+        <v>380000</v>
+      </c>
+      <c r="E76" t="str">
+        <v>330000</v>
+      </c>
+      <c r="F76" s="1">
+        <v>45891.999814814815</v>
+      </c>
+      <c r="G76">
+        <v>75</v>
+      </c>
+      <c r="H76">
+        <v>50000</v>
+      </c>
+      <c r="I76" t="str">
+        <v>Mangata system</v>
+      </c>
+      <c r="J76" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>04456553179</v>
+      </c>
+      <c r="B77">
+        <v>16</v>
+      </c>
+      <c r="C77" t="str">
+        <v>pending</v>
+      </c>
+      <c r="D77" t="str">
+        <v>380000</v>
+      </c>
+      <c r="E77" t="str">
+        <v>330000</v>
+      </c>
+      <c r="F77" s="1">
+        <v>45891.999814814815</v>
+      </c>
+      <c r="G77">
+        <v>76</v>
+      </c>
+      <c r="H77">
+        <v>50000</v>
+      </c>
+      <c r="I77" t="str">
+        <v>Mangata system</v>
+      </c>
+      <c r="J77" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>91202465562</v>
+      </c>
+      <c r="B78">
+        <v>16</v>
+      </c>
+      <c r="C78" t="str">
+        <v>pending</v>
+      </c>
+      <c r="D78" t="str">
+        <v>380000</v>
+      </c>
+      <c r="E78" t="str">
+        <v>330000</v>
+      </c>
+      <c r="F78" s="1">
+        <v>45891.999814814815</v>
+      </c>
+      <c r="G78">
+        <v>77</v>
+      </c>
+      <c r="H78">
+        <v>50000</v>
+      </c>
+      <c r="I78" t="str">
+        <v>Mangata system</v>
+      </c>
+      <c r="J78" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>87490073686</v>
+      </c>
+      <c r="B79">
+        <v>16</v>
+      </c>
+      <c r="C79" t="str">
+        <v>pending</v>
+      </c>
+      <c r="D79" t="str">
+        <v>380000</v>
+      </c>
+      <c r="E79" t="str">
+        <v>330000</v>
+      </c>
+      <c r="F79" s="1">
+        <v>45891.999814814815</v>
+      </c>
+      <c r="G79">
+        <v>78</v>
+      </c>
+      <c r="H79">
+        <v>50000</v>
+      </c>
+      <c r="I79" t="str">
+        <v>Mangata system</v>
+      </c>
+      <c r="J79" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>80734578230</v>
+      </c>
+      <c r="B80">
+        <v>16</v>
+      </c>
+      <c r="C80" t="str">
+        <v>pending</v>
+      </c>
+      <c r="D80" t="str">
+        <v>380000</v>
+      </c>
+      <c r="E80" t="str">
+        <v>330000</v>
+      </c>
+      <c r="F80" s="1">
+        <v>45891.999814814815</v>
+      </c>
+      <c r="G80">
+        <v>79</v>
+      </c>
+      <c r="H80">
+        <v>50000</v>
+      </c>
+      <c r="I80" t="str">
+        <v>Mangata system</v>
+      </c>
+      <c r="J80" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>78775911334</v>
+      </c>
+      <c r="B81">
+        <v>16</v>
+      </c>
+      <c r="C81" t="str">
+        <v>pending</v>
+      </c>
+      <c r="D81" t="str">
+        <v>380000</v>
+      </c>
+      <c r="E81" t="str">
+        <v>330000</v>
+      </c>
+      <c r="F81" s="1">
+        <v>45922.999814814815</v>
+      </c>
+      <c r="G81">
+        <v>80</v>
+      </c>
+      <c r="H81">
+        <v>50000</v>
+      </c>
+      <c r="I81" t="str">
+        <v>Mangata system</v>
+      </c>
+      <c r="J81" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>22664360928</v>
+      </c>
+      <c r="B82">
+        <v>16</v>
+      </c>
+      <c r="C82" t="str">
+        <v>pending</v>
+      </c>
+      <c r="D82" t="str">
+        <v>380000</v>
+      </c>
+      <c r="E82" t="str">
+        <v>330000</v>
+      </c>
+      <c r="F82" s="1">
+        <v>45899.999814814815</v>
+      </c>
+      <c r="G82">
+        <v>81</v>
+      </c>
+      <c r="H82">
+        <v>50000</v>
+      </c>
+      <c r="I82" t="str">
+        <v>Mangata system</v>
+      </c>
+      <c r="J82" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>78731599508</v>
+      </c>
+      <c r="B83">
+        <v>16</v>
+      </c>
+      <c r="C83" t="str">
+        <v>pending</v>
+      </c>
+      <c r="D83" t="str">
+        <v>380000</v>
+      </c>
+      <c r="E83" t="str">
+        <v>330000</v>
+      </c>
+      <c r="F83" s="1">
+        <v>45931.999814814815</v>
+      </c>
+      <c r="G83">
+        <v>82</v>
+      </c>
+      <c r="H83">
+        <v>50000</v>
+      </c>
+      <c r="I83" t="str">
+        <v>Mangata system</v>
+      </c>
+      <c r="J83" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>70293992686</v>
+      </c>
+      <c r="B84">
+        <v>16</v>
+      </c>
+      <c r="C84" t="str">
+        <v>approved</v>
+      </c>
+      <c r="D84" t="str">
+        <v>380000</v>
+      </c>
+      <c r="E84" t="str">
+        <v>330000</v>
+      </c>
+      <c r="F84" s="1">
+        <v>45920.999814814815</v>
+      </c>
+      <c r="G84">
+        <v>83</v>
+      </c>
+      <c r="H84">
+        <v>50000</v>
+      </c>
+      <c r="I84" t="str">
+        <v>Mangata system</v>
+      </c>
+      <c r="J84" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>18954208592</v>
+      </c>
+      <c r="B85">
+        <v>16</v>
+      </c>
+      <c r="C85" t="str">
+        <v>approved</v>
+      </c>
+      <c r="D85" t="str">
+        <v>380000</v>
+      </c>
+      <c r="E85" t="str">
+        <v>330000</v>
+      </c>
+      <c r="F85" s="1">
+        <v>45891.999814814815</v>
+      </c>
+      <c r="G85">
+        <v>84</v>
+      </c>
+      <c r="H85">
+        <v>50000</v>
+      </c>
+      <c r="I85" t="str">
+        <v>Mangata system</v>
+      </c>
+      <c r="J85" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>35195651480</v>
+      </c>
+      <c r="B86">
+        <v>16</v>
+      </c>
+      <c r="C86" t="str">
+        <v>pending</v>
+      </c>
+      <c r="D86" t="str">
+        <v>380000</v>
+      </c>
+      <c r="E86" t="str">
+        <v>330000</v>
+      </c>
+      <c r="F86" s="1">
+        <v>45914.999814814815</v>
+      </c>
+      <c r="G86">
+        <v>85</v>
+      </c>
+      <c r="H86">
+        <v>50000</v>
+      </c>
+      <c r="I86" t="str">
+        <v>Mangata system</v>
+      </c>
+      <c r="J86" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>00446720194</v>
+      </c>
+      <c r="B87">
+        <v>16</v>
+      </c>
+      <c r="C87" t="str">
+        <v>pending</v>
+      </c>
+      <c r="D87" t="str">
+        <v>380000</v>
+      </c>
+      <c r="E87" t="str">
+        <v>330000</v>
+      </c>
+      <c r="F87" s="1">
+        <v>45931.999814814815</v>
+      </c>
+      <c r="G87">
+        <v>86</v>
+      </c>
+      <c r="H87">
+        <v>50000</v>
+      </c>
+      <c r="I87" t="str">
+        <v>Mangata system</v>
+      </c>
+      <c r="J87" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K87"/>
   </ignoredErrors>
 </worksheet>
 </file>